--- a/feasibility_outputs/chint_profile_config_run/profile_items.xlsx
+++ b/feasibility_outputs/chint_profile_config_run/profile_items.xlsx
@@ -4500,595 +4500,95 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>supplier_code</t>
+          <t>source_page</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>source_page</t>
+          <t>layout_name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>layout_name</t>
+          <t>product_family</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>product_family</t>
+          <t>type</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>pole</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>pole</t>
+          <t>rated_current</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>rated_current</t>
+          <t>breaking_capacity</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>breaking_capacity</t>
+          <t>material_code</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>material_code</t>
+          <t>description</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>unit_price</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>unit_price</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>confidence</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>extraction_method</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>extraction_method</t>
+          <t>evidence_text</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>evidence_text</t>
+          <t>errors</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>validation_status</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
           <t>warnings</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CHINT</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>chint_mccb_nxm_nm1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>MCCB Chint</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Mã</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>3P</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Iđm(A)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Icu(kA)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Mã</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>MCCB Chint Mã 3P Iđm(A) Icu(kA)</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>coordinate_column_profiler</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Iđm (A) Icu (kA) Mã 2P 3P 4P</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>invalid</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>material_code_invalid_prefix, material_code_invalid_format</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CHINT</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>chint_mccb_nxm_nm1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>MCCB Chint</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Dải</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>3P</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Dải</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>MCCB Chint Dải 3P</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>251250</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>coordinate_column_profiler</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Dải dòng định mức: 25A ÷ 1250A</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>invalid</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>material_code_invalid_prefix, material_code_invalid_format</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CHINT</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>chint_mccb_nxm_nm1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>MCCB Chint</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Điện</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>3P</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Điện</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>MCCB Chint Điện 3P</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>380400415690</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>coordinate_column_profiler</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Điện áp định mức: 380/400/415/690V</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>invalid</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>material_code_invalid_prefix, material_code_invalid_format</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CHINT</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>chint_mccb_nxm_nm1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>MCCB Chint</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Số</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>3P</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Số</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>MCCB Chint Số 3P</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>coordinate_column_profiler</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Số pha: 2P, 3P, 4P</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>invalid</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>material_code_invalid_prefix, material_code_invalid_format</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CHINT</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>chint_mccb_nxm_nm1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>MCCB Chint</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Icu:</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>3P</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Icu:</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>MCCB Chint Icu: 3P</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>65</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>coordinate_column_profiler</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Icu: 20kA tới 65kA (tùy chọn)</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>invalid</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>material_code_invalid_prefix, material_code_invalid_format</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CHINT</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>chint_mccb_nxm_nm1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>MCCB Chint</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Mã</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>3P</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Iđm(A)</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Icu(kA)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Mã</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>MCCB Chint Mã 3P Iđm(A) Icu(kA)</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>coordinate_column_profiler</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Iđm (A) Icu (kA) Mã 2P 3P 4P</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>invalid</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>material_code_invalid_prefix, material_code_invalid_format</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
